--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/07,26/06,07,26 Останкино КИ/дв 06,07,26 лгрсч ост ки.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/07,26/06,07,26 Останкино КИ/дв 06,07,26 лгрсч ост ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчет Останкино КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\07,26\06,07,26 Останкино КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA457950-5753-4545-A356-9C7866C8E760}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73CD7E85-12AD-4404-96B1-4509A929AD4E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AD$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AD$98</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="141">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -449,6 +449,52 @@
   </si>
   <si>
     <t>13,07,</t>
+  </si>
+  <si>
+    <t>7647  ХОЧУ ВЕТЧ. ИЗ СВИН.ОТРУБА с/н мгс 1/100</t>
+  </si>
+  <si>
+    <t>7651  ХОЧУ ВЕТЧ. МРАМОР. ПМ с/н мгс 1/100_Л11</t>
+  </si>
+  <si>
+    <t>7299  НАБОР ДЛЯ ПИЦЦЫ Папа Может с/к в/у</t>
+  </si>
+  <si>
+    <t>новинка</t>
+  </si>
+  <si>
+    <t>ротация</t>
+  </si>
+  <si>
+    <t>ротация на 1001062507616,ЭКСТРА Папа может с/к с/н в/у 1/100_Л10</t>
+  </si>
+  <si>
+    <t>ротация на 1001061977613,АРОМАТНАЯ с/к с/н в/у 1/100 10шт_Л10</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>нужно увеличить продажи!!!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> / ротация на 1001304197608,СЕРВЕЛАТ ШВЕЙЦАРСК.в/к с/н в/у 1/100_Л11</t>
+    </r>
+  </si>
+  <si>
+    <t>плюсом 5 дней</t>
   </si>
 </sst>
 </file>
@@ -1400,7 +1446,7 @@
       </c>
       <c r="T5" s="3">
         <f t="shared" si="0"/>
-        <v>12529</v>
+        <v>13579</v>
       </c>
       <c r="U5" s="8"/>
       <c r="V5" s="8"/>
@@ -1431,7 +1477,7 @@
       <c r="AC5" s="8"/>
       <c r="AD5" s="3">
         <f>SUM(AD6:AD500)</f>
-        <v>5973.0000000000018</v>
+        <v>6123.0000000000018</v>
       </c>
       <c r="AE5" s="8"/>
       <c r="AF5" s="8"/>
@@ -1638,7 +1684,9 @@
       <c r="AB7" s="8">
         <v>1.4690000000000001</v>
       </c>
-      <c r="AC7" s="8"/>
+      <c r="AC7" s="8" t="s">
+        <v>140</v>
+      </c>
       <c r="AD7" s="8">
         <f t="shared" ref="AD7:AD70" si="8">G7*T7</f>
         <v>6</v>
@@ -1741,7 +1789,9 @@
       <c r="AB8" s="8">
         <v>11.2</v>
       </c>
-      <c r="AC8" s="8"/>
+      <c r="AC8" s="8" t="s">
+        <v>140</v>
+      </c>
       <c r="AD8" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -1955,7 +2005,9 @@
       <c r="AB10" s="8">
         <v>5.0541999999999998</v>
       </c>
-      <c r="AC10" s="8"/>
+      <c r="AC10" s="8" t="s">
+        <v>140</v>
+      </c>
       <c r="AD10" s="8">
         <f t="shared" si="8"/>
         <v>20</v>
@@ -2269,7 +2321,9 @@
       <c r="AB13" s="8">
         <v>6.6</v>
       </c>
-      <c r="AC13" s="8"/>
+      <c r="AC13" s="8" t="s">
+        <v>140</v>
+      </c>
       <c r="AD13" s="8">
         <f t="shared" si="8"/>
         <v>32</v>
@@ -2483,7 +2537,9 @@
       <c r="AB15" s="8">
         <v>18.600000000000001</v>
       </c>
-      <c r="AC15" s="8"/>
+      <c r="AC15" s="8" t="s">
+        <v>140</v>
+      </c>
       <c r="AD15" s="8">
         <f t="shared" si="8"/>
         <v>5</v>
@@ -2799,7 +2855,9 @@
       <c r="AB18" s="8">
         <v>5.4109999999999996</v>
       </c>
-      <c r="AC18" s="8"/>
+      <c r="AC18" s="8" t="s">
+        <v>140</v>
+      </c>
       <c r="AD18" s="8">
         <f t="shared" si="8"/>
         <v>25</v>
@@ -3114,7 +3172,9 @@
       <c r="AB21" s="8">
         <v>27.2</v>
       </c>
-      <c r="AC21" s="8"/>
+      <c r="AC21" s="8" t="s">
+        <v>140</v>
+      </c>
       <c r="AD21" s="8">
         <f t="shared" si="8"/>
         <v>180.4</v>
@@ -4342,8 +4402,8 @@
       <c r="H33" s="8">
         <v>60</v>
       </c>
-      <c r="I33" s="8">
-        <v>6453</v>
+      <c r="I33" s="8" t="s">
+        <v>136</v>
       </c>
       <c r="J33" s="8"/>
       <c r="K33" s="8">
@@ -4400,7 +4460,9 @@
       <c r="AB33" s="8">
         <v>31.8</v>
       </c>
-      <c r="AC33" s="8"/>
+      <c r="AC33" s="8" t="s">
+        <v>137</v>
+      </c>
       <c r="AD33" s="8">
         <f t="shared" si="8"/>
         <v>76.2</v>
@@ -4450,8 +4512,8 @@
       <c r="H34" s="8">
         <v>60</v>
       </c>
-      <c r="I34" s="8">
-        <v>6454</v>
+      <c r="I34" s="8" t="s">
+        <v>136</v>
       </c>
       <c r="J34" s="8"/>
       <c r="K34" s="8">
@@ -4508,7 +4570,9 @@
       <c r="AB34" s="8">
         <v>42.2</v>
       </c>
-      <c r="AC34" s="8"/>
+      <c r="AC34" s="8" t="s">
+        <v>138</v>
+      </c>
       <c r="AD34" s="8">
         <f t="shared" si="8"/>
         <v>23.8</v>
@@ -4556,8 +4620,8 @@
       <c r="H35" s="8">
         <v>45</v>
       </c>
-      <c r="I35" s="8">
-        <v>6459</v>
+      <c r="I35" s="8" t="s">
+        <v>136</v>
       </c>
       <c r="J35" s="8"/>
       <c r="K35" s="8">
@@ -4609,8 +4673,8 @@
       <c r="AB35" s="8">
         <v>16.600000000000001</v>
       </c>
-      <c r="AC35" s="14" t="s">
-        <v>35</v>
+      <c r="AC35" s="13" t="s">
+        <v>139</v>
       </c>
       <c r="AD35" s="8">
         <f t="shared" si="8"/>
@@ -8422,7 +8486,7 @@
       </c>
       <c r="AC71" s="8"/>
       <c r="AD71" s="8">
-        <f t="shared" ref="AD71:AD95" si="27">G71*T71</f>
+        <f t="shared" ref="AD71:AD98" si="27">G71*T71</f>
         <v>54.6</v>
       </c>
       <c r="AE71" s="8"/>
@@ -10950,15 +11014,23 @@
       <c r="AW95" s="8"/>
     </row>
     <row r="96" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A96" s="8"/>
-      <c r="B96" s="8"/>
+      <c r="A96" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="B96" s="8" t="s">
+        <v>31</v>
+      </c>
       <c r="C96" s="8"/>
       <c r="D96" s="8"/>
       <c r="E96" s="8"/>
       <c r="F96" s="8"/>
-      <c r="G96" s="6"/>
+      <c r="G96" s="6">
+        <v>0.1</v>
+      </c>
       <c r="H96" s="8"/>
-      <c r="I96" s="8"/>
+      <c r="I96" s="8">
+        <v>7647</v>
+      </c>
       <c r="J96" s="8"/>
       <c r="K96" s="8"/>
       <c r="L96" s="8"/>
@@ -10967,19 +11039,40 @@
       <c r="O96" s="8"/>
       <c r="P96" s="8"/>
       <c r="Q96" s="8"/>
-      <c r="R96" s="8"/>
+      <c r="R96" s="8">
+        <v>0</v>
+      </c>
       <c r="S96" s="8"/>
-      <c r="T96" s="8"/>
+      <c r="T96" s="8">
+        <v>500</v>
+      </c>
       <c r="U96" s="8"/>
       <c r="V96" s="8"/>
-      <c r="W96" s="8"/>
-      <c r="X96" s="8"/>
-      <c r="Y96" s="8"/>
-      <c r="Z96" s="8"/>
-      <c r="AA96" s="8"/>
-      <c r="AB96" s="8"/>
-      <c r="AC96" s="8"/>
-      <c r="AD96" s="8"/>
+      <c r="W96" s="8">
+        <v>0</v>
+      </c>
+      <c r="X96" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="AD96" s="8">
+        <f t="shared" si="27"/>
+        <v>50</v>
+      </c>
       <c r="AE96" s="8"/>
       <c r="AF96" s="8"/>
       <c r="AG96" s="8"/>
@@ -11001,15 +11094,23 @@
       <c r="AW96" s="8"/>
     </row>
     <row r="97" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A97" s="8"/>
-      <c r="B97" s="8"/>
+      <c r="A97" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="B97" s="8" t="s">
+        <v>31</v>
+      </c>
       <c r="C97" s="8"/>
       <c r="D97" s="8"/>
       <c r="E97" s="8"/>
       <c r="F97" s="8"/>
-      <c r="G97" s="6"/>
+      <c r="G97" s="6">
+        <v>0.1</v>
+      </c>
       <c r="H97" s="8"/>
-      <c r="I97" s="8"/>
+      <c r="I97" s="8">
+        <v>7651</v>
+      </c>
       <c r="J97" s="8"/>
       <c r="K97" s="8"/>
       <c r="L97" s="8"/>
@@ -11018,19 +11119,40 @@
       <c r="O97" s="8"/>
       <c r="P97" s="8"/>
       <c r="Q97" s="8"/>
-      <c r="R97" s="8"/>
+      <c r="R97" s="8">
+        <v>0</v>
+      </c>
       <c r="S97" s="8"/>
-      <c r="T97" s="8"/>
+      <c r="T97" s="8">
+        <v>500</v>
+      </c>
       <c r="U97" s="8"/>
       <c r="V97" s="8"/>
-      <c r="W97" s="8"/>
-      <c r="X97" s="8"/>
-      <c r="Y97" s="8"/>
-      <c r="Z97" s="8"/>
-      <c r="AA97" s="8"/>
-      <c r="AB97" s="8"/>
-      <c r="AC97" s="8"/>
-      <c r="AD97" s="8"/>
+      <c r="W97" s="8">
+        <v>0</v>
+      </c>
+      <c r="X97" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB97" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="AD97" s="8">
+        <f t="shared" si="27"/>
+        <v>50</v>
+      </c>
       <c r="AE97" s="8"/>
       <c r="AF97" s="8"/>
       <c r="AG97" s="8"/>
@@ -11052,15 +11174,23 @@
       <c r="AW97" s="8"/>
     </row>
     <row r="98" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A98" s="8"/>
-      <c r="B98" s="8"/>
+      <c r="A98" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="B98" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="C98" s="8"/>
       <c r="D98" s="8"/>
       <c r="E98" s="8"/>
       <c r="F98" s="8"/>
-      <c r="G98" s="6"/>
+      <c r="G98" s="6">
+        <v>1</v>
+      </c>
       <c r="H98" s="8"/>
-      <c r="I98" s="8"/>
+      <c r="I98" s="8">
+        <v>7299</v>
+      </c>
       <c r="J98" s="8"/>
       <c r="K98" s="8"/>
       <c r="L98" s="8"/>
@@ -11069,19 +11199,40 @@
       <c r="O98" s="8"/>
       <c r="P98" s="8"/>
       <c r="Q98" s="8"/>
-      <c r="R98" s="8"/>
+      <c r="R98" s="8">
+        <v>0</v>
+      </c>
       <c r="S98" s="8"/>
-      <c r="T98" s="8"/>
+      <c r="T98" s="8">
+        <v>50</v>
+      </c>
       <c r="U98" s="8"/>
       <c r="V98" s="8"/>
-      <c r="W98" s="8"/>
-      <c r="X98" s="8"/>
-      <c r="Y98" s="8"/>
-      <c r="Z98" s="8"/>
-      <c r="AA98" s="8"/>
-      <c r="AB98" s="8"/>
-      <c r="AC98" s="8"/>
-      <c r="AD98" s="8"/>
+      <c r="W98" s="8">
+        <v>0</v>
+      </c>
+      <c r="X98" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA98" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB98" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="AD98" s="8">
+        <f t="shared" si="27"/>
+        <v>50</v>
+      </c>
       <c r="AE98" s="8"/>
       <c r="AF98" s="8"/>
       <c r="AG98" s="8"/>
@@ -31605,7 +31756,7 @@
       <c r="AW500" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AD95" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:AD98" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
